--- a/data/trans_camb/P32A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,77</t>
+          <t>-1,18; 1,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,15</t>
+          <t>-1,17; 2,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,12</t>
+          <t>-1,28; 2,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,58</t>
+          <t>0,58; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,42</t>
+          <t>-0,24; 2,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,03</t>
+          <t>-0,47; 1,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,63</t>
+          <t>-0,61; 1,71</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 499,75</t>
+          <t>-67,55; 578,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,03; 626,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 635,47</t>
+          <t>-83,14; 635,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 833,72</t>
+          <t>-39,05; 941,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,01; 938,72</t>
+          <t>-56,76; 742,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,81; 593,29</t>
+          <t>-59,19; 668,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,14</t>
+          <t>-0,15; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,92</t>
+          <t>0,51; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,35</t>
+          <t>-0,44; 2,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,46</t>
+          <t>0,29; 2,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,05</t>
+          <t>1,2; 5,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,15</t>
+          <t>-0,0; 2,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,89</t>
+          <t>0,66; 2,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,68</t>
+          <t>0,52; 2,82</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 1203,67</t>
+          <t>-26,89; 872,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 1014,1</t>
+          <t>14,65; 1067,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 638,68</t>
+          <t>-49,93; 595,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 850,51</t>
+          <t>-18,66; 942,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,96; 1143,33</t>
+          <t>58,51; 1504,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 1052,42</t>
+          <t>37,35; 1238,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,95</t>
+          <t>-1,16; 3,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,84</t>
+          <t>-2,31; 1,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,77</t>
+          <t>-2,98; 1,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,0</t>
+          <t>-3,54; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,83</t>
+          <t>-2,81; 0,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,74</t>
+          <t>-2,02; 2,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,46</t>
+          <t>-1,27; 2,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,02</t>
+          <t>-1,87; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,05</t>
+          <t>-2,34; 0,99</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 339,74</t>
+          <t>-40,2; 295,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,71; 193,34</t>
+          <t>-69,74; 174,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,88; 93,49</t>
+          <t>-83,81; 148,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 216,86</t>
+          <t>-47,24; 214,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 118,33</t>
+          <t>-71,0; 121,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-81,29; 116,67</t>
+          <t>-84,86; 98,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,23</t>
+          <t>1,2; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,23</t>
+          <t>-0,12; 2,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,75</t>
+          <t>0,68; 3,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,23</t>
+          <t>-1,01; 2,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,72</t>
+          <t>-0,05; 3,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,58</t>
+          <t>-1,01; 1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,85</t>
+          <t>0,76; 2,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,24</t>
+          <t>0,33; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,54</t>
+          <t>0,38; 2,46</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>98,67; 2246,08</t>
+          <t>66,51; 2286,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 1118,73</t>
+          <t>-42,17; 1486,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,43; —</t>
+          <t>22,54; 1944,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,21; —</t>
+          <t>-46,03; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,69; —</t>
+          <t>-83,15; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,68; 1168,92</t>
+          <t>51,99; 1164,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 1039,44</t>
+          <t>8,1; 901,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,51; 1063,15</t>
+          <t>20,48; 887,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,44</t>
+          <t>0,7; 2,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,79</t>
+          <t>0,22; 1,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,5</t>
+          <t>0,02; 1,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,32</t>
+          <t>-0,12; 1,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,91</t>
+          <t>0,35; 1,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,15</t>
+          <t>0,09; 2,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,85</t>
+          <t>0,54; 1,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,48</t>
+          <t>0,37; 1,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,15; 1,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>35,22; 313,78</t>
+          <t>45,47; 329,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2,89; 243,6</t>
+          <t>12,23; 231,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 209,32</t>
+          <t>-5,71; 205,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 1060,29</t>
+          <t>-61,07; 1054,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1561,1</t>
+          <t>19,66; 1672,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1608,61</t>
+          <t>-6,28; 1461,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,1; 301,28</t>
+          <t>44,22; 296,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>34,53; 244,29</t>
+          <t>35,33; 257,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,35; 244,66</t>
+          <t>12,4; 232,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,95</t>
+          <t>-1,14; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,24</t>
+          <t>-1,21; 2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,2</t>
+          <t>-1,37; 1,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,01</t>
+          <t>0,58; 5,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,42</t>
+          <t>-0,3; 2,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,98</t>
+          <t>-0,53; 1,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,71</t>
+          <t>-0,85; 1,51</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 578,66</t>
+          <t>-73,14; 606,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-80,63; 550,08</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-77,87; 488,96</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-83,14; 635,91</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 941,33</t>
+          <t>-46,54; 707,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,76; 742,07</t>
+          <t>-52,13; 740,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,19; 668,88</t>
+          <t>-72,59; 573,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,06</t>
+          <t>-0,24; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,74</t>
+          <t>0,65; 3,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,16</t>
+          <t>-0,56; 2,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,8</t>
+          <t>0,29; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,98</t>
+          <t>1,24; 6,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,18</t>
+          <t>-0,08; 2,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,89</t>
+          <t>0,58; 2,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,82</t>
+          <t>0,41; 2,66</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>242,2%</t>
+          <t>242,47%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 872,77</t>
+          <t>-40,25; 867,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 1067,44</t>
+          <t>20,62; 1147,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 595,27</t>
+          <t>-50,91; 578,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 942,36</t>
+          <t>-33,95; 849,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,51; 1504,46</t>
+          <t>29,11; 1150,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,35; 1238,49</t>
+          <t>22,79; 967,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,68</t>
+          <t>-1,34; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,8</t>
+          <t>-2,63; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,08</t>
+          <t>-2,88; 1,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,0</t>
+          <t>-3,57; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,83</t>
+          <t>-2,84; 0,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,98</t>
+          <t>0,07; 7,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,23</t>
+          <t>-1,19; 2,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,07</t>
+          <t>-2,04; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,99</t>
+          <t>-1,31; 2,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-44,72%</t>
+          <t>-25,07%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>353,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,79%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 295,14</t>
+          <t>-40,83; 334,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 174,4</t>
+          <t>-74,53; 166,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,81; 148,02</t>
+          <t>-77,76; 124,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 214,44</t>
+          <t>-47,55; 232,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,0; 121,9</t>
+          <t>-72,92; 130,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,86; 98,69</t>
+          <t>-52,76; 214,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,18</t>
+          <t>1,22; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,23</t>
+          <t>-0,16; 2,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,76</t>
+          <t>0,68; 3,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,19</t>
+          <t>-0,92; 2,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,69</t>
+          <t>-0,26; 3,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,55</t>
+          <t>-0,32; 3,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,96</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,39</t>
+          <t>0,29; 2,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,46</t>
+          <t>0,56; 3,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>403,09%</t>
+          <t>393,26%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>163,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>246,7%</t>
+          <t>288,66%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>66,51; 2286,24</t>
+          <t>81,16; 2261,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 1486,48</t>
+          <t>-47,47; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,54; 1944,55</t>
+          <t>11,71; 2178,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,03; —</t>
+          <t>-61,9; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,15; —</t>
+          <t>-73,23; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,99; 1164,7</t>
+          <t>52,32; 1159,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,1; 901,57</t>
+          <t>9,89; 938,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,48; 887,07</t>
+          <t>31,25; 1326,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>1,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,44</t>
+          <t>0,67; 2,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,83</t>
+          <t>0,13; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,57</t>
+          <t>0,03; 1,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,34</t>
+          <t>-0,12; 1,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,85</t>
+          <t>0,28; 1,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,02</t>
+          <t>0,87; 3,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,78</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,41</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>317,94%</t>
+          <t>551,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>133,22%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45,47; 329,99</t>
+          <t>37,81; 318,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,23; 231,6</t>
+          <t>6,24; 232,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 205,86</t>
+          <t>-0,85; 199,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 1054,78</t>
+          <t>-45,93; 1299,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,66; 1672,48</t>
+          <t>0,08; 1448,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1461,11</t>
+          <t>98,61; 2466,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,22; 296,91</t>
+          <t>42,03; 280,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>35,33; 257,56</t>
+          <t>29,33; 239,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,4; 232,86</t>
+          <t>43,54; 301,36</t>
         </is>
       </c>
     </row>
